--- a/data/satisfaction_detail/2026/Q3/参展商.xlsx
+++ b/data/satisfaction_detail/2026/Q3/参展商.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.681162790697673</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>9.745116279069768</v>
